--- a/event_planner_forms/024_event_notification_form--event_planner_forms.xlsx
+++ b/event_planner_forms/024_event_notification_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -885,8 +885,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -914,12 +914,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'police'}</t>
+          <t>police</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Police'}</t>
+          <t>Police</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'mayor'}</t>
+          <t>mayor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Mayor'}</t>
+          <t>Mayor</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'fire_department'}</t>
+          <t>fire_department</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Fire Department'}</t>
+          <t>Fire Department</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'meeting'}</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Meeting'}</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'concert'}</t>
+          <t>concert</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Concert'}</t>
+          <t>Concert</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'wedding'}</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Wedding'}</t>
+          <t>Wedding</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'chatjimmy2'}</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'reopened'}</t>
+          <t>reopened</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'Reopened'}</t>
+          <t>Reopened</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
